--- a/Attendance/Attendance - Daily DSA TY.xlsx
+++ b/Attendance/Attendance - Daily DSA TY.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB72802B-36F1-48CD-9C91-0A48BECA72C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFA5E9A-7445-4B78-9E11-01F1B3D2BFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17678C9F-2FE9-440B-883F-25FBE88BD6F2}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="96">
   <si>
     <t>S. No.</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>11 Jul PM</t>
+  </si>
+  <si>
+    <t>13 Jul PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rudra  sandip sinde  </t>
   </si>
 </sst>
 </file>
@@ -660,13 +666,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8080B9-1F79-4EA3-BF5D-949EC22A7384}">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,8 +730,11 @@
       <c r="S1" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -769,7 +778,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -813,7 +822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -857,7 +866,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -901,7 +910,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -945,7 +954,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -995,7 +1004,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1039,7 +1048,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1083,7 +1092,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1127,7 +1136,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1171,7 +1180,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1215,7 +1224,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1259,7 +1268,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1303,7 +1312,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1391,7 +1400,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1435,7 +1444,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1479,7 +1488,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1523,7 +1532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1573,7 +1582,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1617,7 +1626,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1661,7 +1670,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1705,7 +1714,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1763,8 +1772,11 @@
       <c r="S24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1816,8 +1828,11 @@
       <c r="Q25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1861,7 +1876,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1914,7 +1929,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1970,7 +1985,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2023,7 +2038,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2075,8 +2090,11 @@
       <c r="Q30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2132,7 +2150,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2176,7 +2194,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2219,8 +2237,11 @@
       <c r="P33" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2264,7 +2285,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2305,7 +2326,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2349,7 +2370,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2393,7 +2414,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2437,7 +2458,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2480,8 +2501,11 @@
       <c r="Q39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2528,7 +2552,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2575,7 +2599,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2616,7 +2640,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2657,7 +2681,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2707,7 +2731,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2745,7 +2769,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2783,7 +2807,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2821,7 +2845,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2874,7 +2898,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2915,7 +2939,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2959,7 +2983,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3011,8 +3035,11 @@
       <c r="R51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3056,7 +3083,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3100,7 +3127,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3145,6 +3172,26 @@
       </c>
       <c r="R54" t="s">
         <v>92</v>
+      </c>
+      <c r="T54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55">
+        <v>241109005</v>
+      </c>
+      <c r="E55" t="s">
+        <v>33</v>
+      </c>
+      <c r="T55" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
